--- a/artfynd/A 43609-2025 artfynd.xlsx
+++ b/artfynd/A 43609-2025 artfynd.xlsx
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>54898601</v>
+        <v>54898619</v>
       </c>
       <c r="B2" t="n">
-        <v>73593</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75422</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1458</v>
+        <v>137</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grå skärelav</t>
+          <t>Liten sönderfallslav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dendrographa decolorans</t>
+          <t>Bactrospora corticola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Turner &amp; Borrer ex Sm.) Ertz &amp; Tehler</t>
+          <t>(Nyl.) Almq.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -717,10 +712,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>554520.4781650226</v>
+        <v>554520</v>
       </c>
       <c r="R2" t="n">
-        <v>6218490.356784763</v>
+        <v>6218490</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -750,24 +745,14 @@
           <t>2015-08-20</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2015-08-20</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>På flera ekar</t>
+          <t>Rikligt på flera ekar inom hela ekbeståndet, även norrut och en bra bit från angiven lokal.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -794,15 +779,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>54898619</v>
+        <v>54898576</v>
       </c>
       <c r="B3" t="n">
-        <v>73625</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75341</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -810,21 +790,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>137</v>
+        <v>1114</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Liten sönderfallslav</t>
+          <t>Gammelekslav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bactrospora corticola</t>
+          <t>Lecanographa amylacea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Almq.</t>
+          <t>(Ehrh. ex Pers.) Egea &amp; Torrente</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -836,10 +816,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>554520.4781650226</v>
+        <v>554520</v>
       </c>
       <c r="R3" t="n">
-        <v>6218490.356784763</v>
+        <v>6218490</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -869,24 +849,14 @@
           <t>2015-08-20</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2015-08-20</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Rikligt på flera ekar inom hela ekbeståndet, även norrut och en bra bit från angiven lokal.</t>
+          <t>En bål på ek</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -913,15 +883,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>54898624</v>
+        <v>54898601</v>
       </c>
       <c r="B4" t="n">
-        <v>73507</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75390</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -929,21 +894,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6428</v>
+        <v>1458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Grå skärelav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Dendrographa decolorans</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Turner &amp; Borrer ex Sm.) Ertz &amp; Tehler</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -955,10 +920,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>554520.4781650226</v>
+        <v>554520</v>
       </c>
       <c r="R4" t="n">
-        <v>6218490.356784763</v>
+        <v>6218490</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -988,24 +953,14 @@
           <t>2015-08-20</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2015-08-20</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Sparsamt på ek</t>
+          <t>På flera ekar</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1032,15 +987,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>54898576</v>
+        <v>54898597</v>
       </c>
       <c r="B5" t="n">
-        <v>73548</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75412</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1048,21 +998,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1114</v>
+        <v>1460</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gammelekslav</t>
+          <t>Rosa skärelav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lecanographa amylacea</t>
+          <t>Schismatomma pericleum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ehrh. ex Pers.) Egea &amp; Torrente</t>
+          <t>(Ach.) Branth &amp; Rostr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1074,10 +1024,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>554520.4781650226</v>
+        <v>554520</v>
       </c>
       <c r="R5" t="n">
-        <v>6218490.356784763</v>
+        <v>6218490</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1107,24 +1057,14 @@
           <t>2015-08-20</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2015-08-20</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>En bål på ek</t>
+          <t>Sparsamt på en ek. Arten är mycket sällsynt i Blekinge och känd från färre än 10 lokaler.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1151,37 +1091,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>54898597</v>
+        <v>54898624</v>
       </c>
       <c r="B6" t="n">
-        <v>73615</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>75300</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1460</v>
+        <v>6428</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rosa skärelav</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Schismatomma pericleum</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Branth &amp; Rostr.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1193,10 +1128,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>554520.4781650226</v>
+        <v>554520</v>
       </c>
       <c r="R6" t="n">
-        <v>6218490.356784763</v>
+        <v>6218490</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1226,24 +1161,14 @@
           <t>2015-08-20</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2015-08-20</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Sparsamt på en ek. Arten är mycket sällsynt i Blekinge och känd från färre än 10 lokaler.</t>
+          <t>Sparsamt på ek</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 43609-2025 artfynd.xlsx
+++ b/artfynd/A 43609-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -776,6 +781,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54898619</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -880,6 +890,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54898576</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -984,6 +999,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54898601</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1088,6 +1108,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54898597</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1192,8 +1217,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54898624</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>